--- a/demo/Results_chocolate/Statistics.xlsx
+++ b/demo/Results_chocolate/Statistics.xlsx
@@ -481,35 +481,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>6.41214370406</v>
+        <v>7.803583906900001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3175041579428061</v>
+        <v>0.4193414282501612</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02592410593906379</v>
+        <v>0.04193414282501612</v>
       </c>
       <c r="G2" t="n">
-        <v>6.419576522</v>
+        <v>7.794794697</v>
       </c>
       <c r="H2" t="n">
-        <v>6.22099304775</v>
+        <v>7.48206751575</v>
       </c>
       <c r="I2" t="n">
-        <v>6.623598159</v>
+        <v>8.03838243625</v>
       </c>
       <c r="J2" t="n">
-        <v>6.361332456419435</v>
+        <v>7.72139298696297</v>
       </c>
       <c r="K2" t="n">
-        <v>6.462954951700565</v>
+        <v>7.885774826837032</v>
       </c>
     </row>
     <row r="3">
@@ -520,35 +520,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D3" t="n">
-        <v>7.803583906900001</v>
+        <v>6.41214370406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4193414282501612</v>
+        <v>0.3175041579428061</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04193414282501612</v>
+        <v>0.02592410593906379</v>
       </c>
       <c r="G3" t="n">
-        <v>7.794794697</v>
+        <v>6.419576522</v>
       </c>
       <c r="H3" t="n">
-        <v>7.48206751575</v>
+        <v>6.22099304775</v>
       </c>
       <c r="I3" t="n">
-        <v>8.03838243625</v>
+        <v>6.623598159</v>
       </c>
       <c r="J3" t="n">
-        <v>7.72139298696297</v>
+        <v>6.361332456419435</v>
       </c>
       <c r="K3" t="n">
-        <v>7.885774826837032</v>
+        <v>6.462954951700565</v>
       </c>
     </row>
     <row r="4">
@@ -559,35 +559,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>6.40062798358</v>
+        <v>7.813202788460001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3175825923436859</v>
+        <v>0.4199229650329013</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02593051008107834</v>
+        <v>0.04199229650329013</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4042741165</v>
+        <v>7.792903781</v>
       </c>
       <c r="H4" t="n">
-        <v>6.20006037025</v>
+        <v>7.49092002425</v>
       </c>
       <c r="I4" t="n">
-        <v>6.606066912499999</v>
+        <v>8.05353251475</v>
       </c>
       <c r="J4" t="n">
-        <v>6.349804183821086</v>
+        <v>7.730897887313552</v>
       </c>
       <c r="K4" t="n">
-        <v>6.451451783338913</v>
+        <v>7.89550768960645</v>
       </c>
     </row>
     <row r="5">
@@ -598,35 +598,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D5" t="n">
-        <v>7.813202788460001</v>
+        <v>6.40062798358</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4199229650329013</v>
+        <v>0.3175825923436859</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04199229650329013</v>
+        <v>0.02593051008107834</v>
       </c>
       <c r="G5" t="n">
-        <v>7.792903781</v>
+        <v>6.4042741165</v>
       </c>
       <c r="H5" t="n">
-        <v>7.49092002425</v>
+        <v>6.20006037025</v>
       </c>
       <c r="I5" t="n">
-        <v>8.05353251475</v>
+        <v>6.606066912499999</v>
       </c>
       <c r="J5" t="n">
-        <v>7.730897887313552</v>
+        <v>6.349804183821086</v>
       </c>
       <c r="K5" t="n">
-        <v>7.89550768960645</v>
+        <v>6.451451783338913</v>
       </c>
     </row>
   </sheetData>
